--- a/Punctuation/data/subset_puntuation.xlsx
+++ b/Punctuation/data/subset_puntuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\paula\OTROS\TFG_repo\Punctuation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C78B6DA-930E-4ADE-A572-2BF1AEA51569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90BE772-CAB0-4928-BE6B-6F47E5782BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{4DD2AA4A-FFB2-45BB-AA1D-F63FA651B14A}"/>
   </bookViews>
@@ -804,7 +804,7 @@
   <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.86328125" customWidth="1"/>
+    <col min="1" max="1" width="31.796875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
   </cols>
   <sheetData>
